--- a/config/pvpandpve.xlsx
+++ b/config/pvpandpve.xlsx
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>報酬ダンジョン</t>
+          <t>奖励地牢</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>依頼任務</t>
+          <t>委托任务</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>時空激戦</t>
+          <t>时空激战</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>パートナー挑戦</t>
+          <t>合作伙伴挑战</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ギルド戦</t>
+          <t>公会战</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>リアルタイム対戦</t>
+          <t>实时对战</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>クロスレイド</t>
+          <t>十字星</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
